--- a/sources/2A_Manha_1_Bimestre.xlsx
+++ b/sources/2A_Manha_1_Bimestre.xlsx
@@ -339,6 +339,12 @@
     <x:t>52%</x:t>
   </x:si>
   <x:si>
+    <x:t>GUILHERME FELIX RIBEIRO MONTEIRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0%</x:t>
+  </x:si>
+  <x:si>
     <x:t>GUILHERME OLIVEIRA DA SILVA</x:t>
   </x:si>
   <x:si>
@@ -414,6 +420,12 @@
     <x:t>LEONARDO DE SOUZA ARAUJO</x:t>
   </x:si>
   <x:si>
+    <x:t>LUCAS DA SILVA CREPALDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98%</x:t>
+  </x:si>
+  <x:si>
     <x:t>LUCAS MASSI AGUENA</x:t>
   </x:si>
   <x:si>
@@ -432,9 +444,6 @@
     <x:t>PEDRO HENRIQUE SOUZA BOMBARDA</x:t>
   </x:si>
   <x:si>
-    <x:t>98%</x:t>
-  </x:si>
-  <x:si>
     <x:t>PEDRO HENRIQUE SOUZA MENDES</x:t>
   </x:si>
   <x:si>
@@ -459,9 +468,18 @@
     <x:t>RAFAELA SANTIAGO DE MORAES</x:t>
   </x:si>
   <x:si>
+    <x:t>RAQUEL RAMOS FERREIRA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93%</x:t>
+  </x:si>
+  <x:si>
     <x:t>RENAN ALAN DOS SANTOS</x:t>
   </x:si>
   <x:si>
+    <x:t>RENIKE WENANCYO SILVA ARAUJO</x:t>
+  </x:si>
+  <x:si>
     <x:t>TAYANE EDUARDA REIS DE LIMA RIBEIRO</x:t>
   </x:si>
   <x:si>
@@ -471,9 +489,6 @@
     <x:t>VINICIUS DO NASCIMENTO RODRIGUES</x:t>
   </x:si>
   <x:si>
-    <x:t>93%</x:t>
-  </x:si>
-  <x:si>
     <x:t>VITOR ARAUJO DE SOUZA FERREIRA</x:t>
   </x:si>
   <x:si>
@@ -481,21 +496,6 @@
   </x:si>
   <x:si>
     <x:t>YRAN CHRISTYAN ALVES DO NASCIMENTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAQUEL RAMOS FERREIRA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUCAS DA SILVA CREPALDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RENIKE WENANCYO SILVA ARAUJO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME FELIX RIBEIRO MONTEIRO</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> </x:t>
@@ -4469,181 +4469,181 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D29" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E29" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="H29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I29" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="L29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="O29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P29" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="S29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="T29" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U29" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="W29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="X29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AA29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AB29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AE29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AF29" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG29" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AI29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AJ29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK29" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AM29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AN29" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO29" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP29" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AQ29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AR29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS29" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AU29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AV29" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW29" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AX29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AY29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AZ29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA29" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BB29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BC29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="BD29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BF29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BG29" s="12">
-        <x:v>42</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH29" s="12" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="BI29" s="12">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ29" s="12" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="BI29" s="12">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="BJ29" s="12" t="s">
-        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:62">
@@ -4651,16 +4651,16 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E30" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F30" s="12" t="s">
         <x:v>49</x:v>
@@ -4669,10 +4669,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I30" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J30" s="12" t="s">
         <x:v>49</x:v>
@@ -4681,10 +4681,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="L30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M30" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N30" s="12" t="s">
         <x:v>49</x:v>
@@ -4693,10 +4693,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="P30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q30" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R30" s="12" t="s">
         <x:v>49</x:v>
@@ -4705,10 +4705,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="T30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U30" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="V30" s="12" t="s">
         <x:v>49</x:v>
@@ -4717,10 +4717,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="X30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z30" s="12" t="s">
         <x:v>49</x:v>
@@ -4729,7 +4729,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AB30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC30" s="12" t="s">
         <x:v>59</x:v>
@@ -4741,7 +4741,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AF30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG30" s="12" t="s">
         <x:v>55</x:v>
@@ -4753,10 +4753,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AJ30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK30" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL30" s="12" t="s">
         <x:v>49</x:v>
@@ -4765,19 +4765,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AN30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO30" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AP30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AQ30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="AR30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS30" s="12" t="s">
         <x:v>62</x:v>
@@ -4789,10 +4789,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AV30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW30" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX30" s="12" t="s">
         <x:v>49</x:v>
@@ -4801,10 +4801,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AZ30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA30" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BB30" s="12" t="s">
         <x:v>49</x:v>
@@ -4813,42 +4813,42 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="BD30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE30" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF30" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG30" s="12">
-        <x:v>76</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="BH30" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BI30" s="12">
-        <x:v>76</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="BJ30" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:62">
       <x:c r="A31" s="11" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F31" s="12" t="s">
         <x:v>49</x:v>
@@ -4857,22 +4857,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H31" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I31" s="12" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="I31" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="J31" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="L31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M31" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N31" s="12" t="s">
         <x:v>49</x:v>
@@ -4881,22 +4881,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="P31" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="T31" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="V31" s="12" t="s">
         <x:v>49</x:v>
@@ -4905,10 +4905,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="X31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z31" s="12" t="s">
         <x:v>49</x:v>
@@ -4917,10 +4917,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AB31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD31" s="12" t="s">
         <x:v>49</x:v>
@@ -4929,7 +4929,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AF31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG31" s="12" t="s">
         <x:v>55</x:v>
@@ -4941,10 +4941,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AJ31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="AL31" s="12" t="s">
         <x:v>49</x:v>
@@ -4953,22 +4953,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AN31" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="AR31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS31" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AT31" s="12" t="s">
         <x:v>49</x:v>
@@ -4977,7 +4977,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AV31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW31" s="12" t="s">
         <x:v>62</x:v>
@@ -4989,10 +4989,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AZ31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA31" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BB31" s="12" t="s">
         <x:v>49</x:v>
@@ -5001,7 +5001,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="BD31" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE31" s="12" t="s">
         <x:v>59</x:v>
@@ -5010,21 +5010,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG31" s="12">
-        <x:v>41</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BH31" s="12" t="s">
-        <x:v>104</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="BI31" s="12">
-        <x:v>36</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BJ31" s="12" t="s">
-        <x:v>86</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:62">
       <x:c r="A32" s="11" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
         <x:v>53</x:v>
@@ -5033,10 +5033,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D32" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F32" s="12" t="s">
         <x:v>49</x:v>
@@ -5048,16 +5048,16 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="I32" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="L32" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M32" s="12" t="s">
         <x:v>59</x:v>
@@ -5069,19 +5069,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="P32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="S32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="T32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="U32" s="12" t="s">
         <x:v>50</x:v>
@@ -5105,10 +5105,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AB32" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC32" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD32" s="12" t="s">
         <x:v>49</x:v>
@@ -5117,10 +5117,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AF32" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG32" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AH32" s="12" t="s">
         <x:v>49</x:v>
@@ -5129,10 +5129,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AJ32" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK32" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AL32" s="12" t="s">
         <x:v>49</x:v>
@@ -5141,7 +5141,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AN32" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO32" s="12" t="s">
         <x:v>50</x:v>
@@ -5156,7 +5156,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AS32" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AT32" s="12" t="s">
         <x:v>49</x:v>
@@ -5165,7 +5165,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AV32" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW32" s="12" t="s">
         <x:v>62</x:v>
@@ -5177,7 +5177,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AZ32" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BA32" s="12" t="s">
         <x:v>63</x:v>
@@ -5198,16 +5198,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG32" s="12">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="BH32" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BI32" s="12">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="BJ32" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:62">
@@ -5221,10 +5221,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D33" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E33" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F33" s="12" t="s">
         <x:v>49</x:v>
@@ -5233,10 +5233,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H33" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I33" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J33" s="12" t="s">
         <x:v>49</x:v>
@@ -5245,10 +5245,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="L33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N33" s="12" t="s">
         <x:v>49</x:v>
@@ -5257,22 +5257,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="P33" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="T33" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V33" s="12" t="s">
         <x:v>49</x:v>
@@ -5281,7 +5281,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="X33" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y33" s="12" t="s">
         <x:v>49</x:v>
@@ -5293,7 +5293,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AB33" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC33" s="12" t="s">
         <x:v>59</x:v>
@@ -5305,10 +5305,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AF33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH33" s="12" t="s">
         <x:v>49</x:v>
@@ -5317,10 +5317,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AJ33" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK33" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL33" s="12" t="s">
         <x:v>49</x:v>
@@ -5329,7 +5329,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AN33" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO33" s="12" t="s">
         <x:v>50</x:v>
@@ -5341,7 +5341,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AR33" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS33" s="12" t="s">
         <x:v>56</x:v>
@@ -5353,10 +5353,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AV33" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AX33" s="12" t="s">
         <x:v>49</x:v>
@@ -5365,10 +5365,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AZ33" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BB33" s="12" t="s">
         <x:v>49</x:v>
@@ -5377,7 +5377,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="BD33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE33" s="12" t="s">
         <x:v>59</x:v>
@@ -5386,13 +5386,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG33" s="12">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="BH33" s="12" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="BI33" s="12">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="BH33" s="12" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="BI33" s="12">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="BJ33" s="12" t="s">
         <x:v>110</x:v>
@@ -5403,16 +5403,16 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F34" s="12" t="s">
         <x:v>49</x:v>
@@ -5421,7 +5421,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I34" s="12" t="s">
         <x:v>63</x:v>
@@ -5433,10 +5433,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="L34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M34" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N34" s="12" t="s">
         <x:v>49</x:v>
@@ -5445,19 +5445,19 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="P34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="S34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="T34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="U34" s="12" t="s">
         <x:v>49</x:v>
@@ -5469,7 +5469,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="X34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y34" s="12" t="s">
         <x:v>49</x:v>
@@ -5481,7 +5481,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AB34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC34" s="12" t="s">
         <x:v>59</x:v>
@@ -5493,10 +5493,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AF34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AG34" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH34" s="12" t="s">
         <x:v>49</x:v>
@@ -5505,10 +5505,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AJ34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AK34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AL34" s="12" t="s">
         <x:v>49</x:v>
@@ -5517,22 +5517,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AN34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO34" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="AR34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT34" s="12" t="s">
         <x:v>49</x:v>
@@ -5541,7 +5541,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AV34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AW34" s="12" t="s">
         <x:v>49</x:v>
@@ -5553,10 +5553,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AZ34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA34" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BB34" s="12" t="s">
         <x:v>49</x:v>
@@ -5565,7 +5565,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="BD34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BE34" s="12" t="s">
         <x:v>59</x:v>
@@ -5574,13 +5574,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG34" s="12">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="BH34" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="BI34" s="12">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="BJ34" s="12" t="s">
         <x:v>112</x:v>
@@ -5591,7 +5591,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C35" s="12">
         <x:v>23</x:v>
@@ -5612,7 +5612,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J35" s="12" t="s">
         <x:v>49</x:v>
@@ -5624,7 +5624,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="M35" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N35" s="12" t="s">
         <x:v>49</x:v>
@@ -5636,7 +5636,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Q35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R35" s="12" t="s">
         <x:v>49</x:v>
@@ -5660,7 +5660,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Y35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z35" s="12" t="s">
         <x:v>49</x:v>
@@ -5672,7 +5672,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AC35" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD35" s="12" t="s">
         <x:v>49</x:v>
@@ -5708,7 +5708,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AO35" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP35" s="12" t="s">
         <x:v>49</x:v>
@@ -5720,7 +5720,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AS35" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT35" s="12" t="s">
         <x:v>49</x:v>
@@ -5732,7 +5732,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AW35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX35" s="12" t="s">
         <x:v>49</x:v>
@@ -5744,7 +5744,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BB35" s="12" t="s">
         <x:v>49</x:v>
@@ -5756,27 +5756,27 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BE35" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF35" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG35" s="12">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BH35" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="BI35" s="12">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BJ35" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:62">
       <x:c r="A36" s="11" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B36" s="12" t="s">
         <x:v>71</x:v>
@@ -5788,7 +5788,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F36" s="12" t="s">
         <x:v>49</x:v>
@@ -5800,7 +5800,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J36" s="12" t="s">
         <x:v>49</x:v>
@@ -5812,7 +5812,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="M36" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N36" s="12" t="s">
         <x:v>49</x:v>
@@ -5836,7 +5836,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="U36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V36" s="12" t="s">
         <x:v>49</x:v>
@@ -5860,7 +5860,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AC36" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD36" s="12" t="s">
         <x:v>49</x:v>
@@ -5872,7 +5872,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AG36" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AH36" s="12" t="s">
         <x:v>49</x:v>
@@ -5884,7 +5884,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AK36" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL36" s="12" t="s">
         <x:v>49</x:v>
@@ -5896,7 +5896,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AO36" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AP36" s="12" t="s">
         <x:v>49</x:v>
@@ -5908,7 +5908,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AS36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AT36" s="12" t="s">
         <x:v>49</x:v>
@@ -5920,7 +5920,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AW36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX36" s="12" t="s">
         <x:v>49</x:v>
@@ -5950,33 +5950,33 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG36" s="12">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="BH36" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BI36" s="12">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="BJ36" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:62">
       <x:c r="A37" s="11" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
         <x:v>49</x:v>
@@ -5985,10 +5985,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H37" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J37" s="12" t="s">
         <x:v>49</x:v>
@@ -5997,7 +5997,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M37" s="12" t="s">
         <x:v>59</x:v>
@@ -6009,22 +6009,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="P37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q37" s="12" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="R37" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="T37" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="V37" s="12" t="s">
         <x:v>49</x:v>
@@ -6033,10 +6033,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="X37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z37" s="12" t="s">
         <x:v>49</x:v>
@@ -6045,10 +6045,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AB37" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD37" s="12" t="s">
         <x:v>49</x:v>
@@ -6057,10 +6057,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AF37" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH37" s="12" t="s">
         <x:v>49</x:v>
@@ -6069,10 +6069,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AJ37" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AL37" s="12" t="s">
         <x:v>49</x:v>
@@ -6081,22 +6081,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AN37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO37" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP37" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="AR37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS37" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AT37" s="12" t="s">
         <x:v>49</x:v>
@@ -6105,10 +6105,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AV37" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AX37" s="12" t="s">
         <x:v>49</x:v>
@@ -6117,10 +6117,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AZ37" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA37" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BB37" s="12" t="s">
         <x:v>49</x:v>
@@ -6129,30 +6129,30 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="BD37" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF37" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG37" s="12">
-        <x:v>17</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="BH37" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BI37" s="12">
-        <x:v>13</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="BJ37" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:62">
       <x:c r="A38" s="11" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
         <x:v>53</x:v>
@@ -6161,7 +6161,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
         <x:v>62</x:v>
@@ -6173,10 +6173,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="H38" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J38" s="12" t="s">
         <x:v>49</x:v>
@@ -6185,10 +6185,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="L38" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N38" s="12" t="s">
         <x:v>49</x:v>
@@ -6197,22 +6197,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="P38" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="S38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="T38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="U38" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V38" s="12" t="s">
         <x:v>49</x:v>
@@ -6221,7 +6221,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="X38" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y38" s="12" t="s">
         <x:v>49</x:v>
@@ -6233,7 +6233,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AB38" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AC38" s="12" t="s">
         <x:v>49</x:v>
@@ -6248,7 +6248,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AG38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH38" s="12" t="s">
         <x:v>49</x:v>
@@ -6260,7 +6260,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AK38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL38" s="12" t="s">
         <x:v>49</x:v>
@@ -6269,7 +6269,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AN38" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO38" s="12" t="s">
         <x:v>50</x:v>
@@ -6293,7 +6293,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AV38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AW38" s="12" t="s">
         <x:v>49</x:v>
@@ -6326,21 +6326,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG38" s="12">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BH38" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="BI38" s="12">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="BJ38" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:62">
       <x:c r="A39" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
         <x:v>53</x:v>
@@ -6349,7 +6349,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D39" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
         <x:v>62</x:v>
@@ -6361,22 +6361,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="H39" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I39" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J39" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="L39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M39" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N39" s="12" t="s">
         <x:v>49</x:v>
@@ -6385,19 +6385,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="P39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q39" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R39" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="T39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U39" s="12" t="s">
         <x:v>62</x:v>
@@ -6409,10 +6409,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="X39" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y39" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z39" s="12" t="s">
         <x:v>49</x:v>
@@ -6421,10 +6421,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AB39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC39" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD39" s="12" t="s">
         <x:v>49</x:v>
@@ -6433,10 +6433,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AF39" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG39" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH39" s="12" t="s">
         <x:v>49</x:v>
@@ -6445,10 +6445,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AJ39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK39" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL39" s="12" t="s">
         <x:v>49</x:v>
@@ -6457,22 +6457,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AN39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO39" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP39" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="AR39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS39" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT39" s="12" t="s">
         <x:v>49</x:v>
@@ -6481,10 +6481,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AV39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW39" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX39" s="12" t="s">
         <x:v>49</x:v>
@@ -6493,10 +6493,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AZ39" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="BA39" s="12" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="BA39" s="12" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="BB39" s="12" t="s">
         <x:v>49</x:v>
@@ -6505,25 +6505,25 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="BD39" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="BE39" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="BE39" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="BF39" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG39" s="12">
-        <x:v>92</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="BH39" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BI39" s="12">
-        <x:v>74</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="BJ39" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:62">
@@ -6537,10 +6537,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D40" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F40" s="12" t="s">
         <x:v>49</x:v>
@@ -6549,22 +6549,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="H40" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I40" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J40" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="L40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M40" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N40" s="12" t="s">
         <x:v>49</x:v>
@@ -6573,22 +6573,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="P40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="S40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="T40" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="V40" s="12" t="s">
         <x:v>49</x:v>
@@ -6597,10 +6597,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="X40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Y40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Z40" s="12" t="s">
         <x:v>49</x:v>
@@ -6609,10 +6609,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AB40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC40" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD40" s="12" t="s">
         <x:v>49</x:v>
@@ -6621,10 +6621,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AF40" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AG40" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="AH40" s="12" t="s">
         <x:v>49</x:v>
@@ -6633,10 +6633,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AJ40" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AK40" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AL40" s="12" t="s">
         <x:v>49</x:v>
@@ -6645,22 +6645,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AN40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AP40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AQ40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="AR40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS40" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AT40" s="12" t="s">
         <x:v>49</x:v>
@@ -6669,10 +6669,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AV40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AX40" s="12" t="s">
         <x:v>49</x:v>
@@ -6681,10 +6681,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AZ40" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BA40" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB40" s="12" t="s">
         <x:v>49</x:v>
@@ -6693,30 +6693,30 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="BD40" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BE40" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BF40" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG40" s="12">
-        <x:v>48</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BH40" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="BI40" s="12">
-        <x:v>44</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="BJ40" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:62">
       <x:c r="A41" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B41" s="12" t="s">
         <x:v>53</x:v>
@@ -6725,7 +6725,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
         <x:v>50</x:v>
@@ -6749,10 +6749,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="L41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M41" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N41" s="12" t="s">
         <x:v>49</x:v>
@@ -6761,22 +6761,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="P41" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q41" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R41" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="S41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="T41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U41" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V41" s="12" t="s">
         <x:v>49</x:v>
@@ -6785,10 +6785,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="X41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y41" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z41" s="12" t="s">
         <x:v>49</x:v>
@@ -6797,10 +6797,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AB41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC41" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD41" s="12" t="s">
         <x:v>49</x:v>
@@ -6812,7 +6812,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AG41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH41" s="12" t="s">
         <x:v>49</x:v>
@@ -6833,22 +6833,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AN41" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO41" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP41" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="AR41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AT41" s="12" t="s">
         <x:v>49</x:v>
@@ -6857,10 +6857,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AV41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AW41" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX41" s="12" t="s">
         <x:v>49</x:v>
@@ -6872,7 +6872,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="BA41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="BB41" s="12" t="s">
         <x:v>49</x:v>
@@ -6881,22 +6881,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="BD41" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BF41" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG41" s="12">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BH41" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="BI41" s="12">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="BJ41" s="12" t="s">
         <x:v>72</x:v>
@@ -6913,10 +6913,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F42" s="12" t="s">
         <x:v>49</x:v>
@@ -6925,10 +6925,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I42" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J42" s="12" t="s">
         <x:v>49</x:v>
@@ -6937,10 +6937,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N42" s="12" t="s">
         <x:v>49</x:v>
@@ -6949,22 +6949,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="P42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Q42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="R42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="S42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="T42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="V42" s="12" t="s">
         <x:v>49</x:v>
@@ -6973,10 +6973,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="X42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Z42" s="12" t="s">
         <x:v>49</x:v>
@@ -6988,7 +6988,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AC42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD42" s="12" t="s">
         <x:v>49</x:v>
@@ -7000,7 +7000,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AG42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH42" s="12" t="s">
         <x:v>49</x:v>
@@ -7009,10 +7009,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AJ42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL42" s="12" t="s">
         <x:v>49</x:v>
@@ -7021,19 +7021,19 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AN42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AO42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AP42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AQ42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="AR42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS42" s="12" t="s">
         <x:v>55</x:v>
@@ -7045,10 +7045,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AV42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AX42" s="12" t="s">
         <x:v>49</x:v>
@@ -7057,7 +7057,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AZ42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA42" s="12" t="s">
         <x:v>55</x:v>
@@ -7069,42 +7069,42 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="BD42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BE42" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BF42" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG42" s="12">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BH42" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="BI42" s="12">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="BJ42" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:62">
       <x:c r="A43" s="11" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B43" s="12" t="s">
-        <x:v>124</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="D43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F43" s="12" t="s">
         <x:v>49</x:v>
@@ -7113,10 +7113,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I43" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J43" s="12" t="s">
         <x:v>49</x:v>
@@ -7125,10 +7125,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="L43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N43" s="12" t="s">
         <x:v>49</x:v>
@@ -7137,10 +7137,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="P43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R43" s="12" t="s">
         <x:v>49</x:v>
@@ -7149,10 +7149,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V43" s="12" t="s">
         <x:v>49</x:v>
@@ -7161,7 +7161,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="X43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y43" s="12" t="s">
         <x:v>49</x:v>
@@ -7173,10 +7173,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AB43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD43" s="12" t="s">
         <x:v>49</x:v>
@@ -7185,10 +7185,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AF43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG43" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH43" s="12" t="s">
         <x:v>49</x:v>
@@ -7197,10 +7197,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AJ43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK43" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL43" s="12" t="s">
         <x:v>49</x:v>
@@ -7209,10 +7209,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AN43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP43" s="12" t="s">
         <x:v>49</x:v>
@@ -7221,10 +7221,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AR43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS43" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AT43" s="12" t="s">
         <x:v>49</x:v>
@@ -7233,10 +7233,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AV43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW43" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX43" s="12" t="s">
         <x:v>49</x:v>
@@ -7245,10 +7245,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AZ43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BA43" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BB43" s="12" t="s">
         <x:v>49</x:v>
@@ -7257,25 +7257,25 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="BD43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BE43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BF43" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG43" s="12">
-        <x:v>39</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="BH43" s="12" t="s">
-        <x:v>86</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="BI43" s="12">
-        <x:v>39</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="BJ43" s="12" t="s">
-        <x:v>86</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:62">
@@ -7283,13 +7283,13 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E44" s="12" t="s">
         <x:v>50</x:v>
@@ -7301,10 +7301,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J44" s="12" t="s">
         <x:v>49</x:v>
@@ -7313,10 +7313,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="L44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M44" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N44" s="12" t="s">
         <x:v>49</x:v>
@@ -7325,22 +7325,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="P44" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q44" s="12" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="R44" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="T44" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="U44" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V44" s="12" t="s">
         <x:v>49</x:v>
@@ -7349,10 +7349,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="X44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y44" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z44" s="12" t="s">
         <x:v>49</x:v>
@@ -7361,10 +7361,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AB44" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC44" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD44" s="12" t="s">
         <x:v>49</x:v>
@@ -7373,10 +7373,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AF44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH44" s="12" t="s">
         <x:v>49</x:v>
@@ -7385,10 +7385,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AJ44" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK44" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL44" s="12" t="s">
         <x:v>49</x:v>
@@ -7397,22 +7397,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AN44" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="AR44" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS44" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT44" s="12" t="s">
         <x:v>49</x:v>
@@ -7421,10 +7421,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AV44" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AX44" s="12" t="s">
         <x:v>49</x:v>
@@ -7433,10 +7433,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AZ44" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BB44" s="12" t="s">
         <x:v>49</x:v>
@@ -7445,25 +7445,25 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="BD44" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE44" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF44" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG44" s="12">
-        <x:v>59</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="BH44" s="12" t="s">
-        <x:v>126</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="BI44" s="12">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="BJ44" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:62">
@@ -7477,10 +7477,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="D45" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F45" s="12" t="s">
         <x:v>49</x:v>
@@ -7489,10 +7489,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H45" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J45" s="12" t="s">
         <x:v>49</x:v>
@@ -7501,10 +7501,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="L45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N45" s="12" t="s">
         <x:v>49</x:v>
@@ -7513,22 +7513,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="P45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="S45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="T45" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="U45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="V45" s="12" t="s">
         <x:v>49</x:v>
@@ -7537,10 +7537,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="X45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z45" s="12" t="s">
         <x:v>49</x:v>
@@ -7549,10 +7549,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AB45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD45" s="12" t="s">
         <x:v>49</x:v>
@@ -7561,10 +7561,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AH45" s="12" t="s">
         <x:v>49</x:v>
@@ -7573,10 +7573,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AJ45" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AK45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AL45" s="12" t="s">
         <x:v>49</x:v>
@@ -7585,22 +7585,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AN45" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AQ45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AR45" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AT45" s="12" t="s">
         <x:v>49</x:v>
@@ -7609,10 +7609,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AV45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AX45" s="12" t="s">
         <x:v>49</x:v>
@@ -7624,7 +7624,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BA45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BB45" s="12" t="s">
         <x:v>49</x:v>
@@ -7633,42 +7633,42 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="BD45" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF45" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG45" s="12">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BH45" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="BI45" s="12">
-        <x:v>0</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BJ45" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:62">
       <x:c r="A46" s="11" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E46" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F46" s="12" t="s">
         <x:v>49</x:v>
@@ -7677,10 +7677,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I46" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J46" s="12" t="s">
         <x:v>49</x:v>
@@ -7689,10 +7689,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="L46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M46" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N46" s="12" t="s">
         <x:v>49</x:v>
@@ -7701,7 +7701,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="P46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q46" s="12" t="s">
         <x:v>49</x:v>
@@ -7713,10 +7713,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="T46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U46" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V46" s="12" t="s">
         <x:v>49</x:v>
@@ -7725,7 +7725,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="X46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y46" s="12" t="s">
         <x:v>49</x:v>
@@ -7737,10 +7737,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AB46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC46" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD46" s="12" t="s">
         <x:v>49</x:v>
@@ -7749,7 +7749,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AF46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AG46" s="12" t="s">
         <x:v>49</x:v>
@@ -7761,10 +7761,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AJ46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK46" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL46" s="12" t="s">
         <x:v>49</x:v>
@@ -7773,10 +7773,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AN46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO46" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP46" s="12" t="s">
         <x:v>49</x:v>
@@ -7785,7 +7785,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AR46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AS46" s="12" t="s">
         <x:v>49</x:v>
@@ -7797,7 +7797,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AV46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AW46" s="12" t="s">
         <x:v>49</x:v>
@@ -7809,7 +7809,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AZ46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA46" s="12" t="s">
         <x:v>49</x:v>
@@ -7821,7 +7821,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="BD46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BE46" s="12" t="s">
         <x:v>49</x:v>
@@ -7830,21 +7830,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG46" s="12">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH46" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="BI46" s="12">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BJ46" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:62">
       <x:c r="A47" s="11" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B47" s="12" t="s">
         <x:v>53</x:v>
@@ -7856,7 +7856,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E47" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F47" s="12" t="s">
         <x:v>49</x:v>
@@ -7865,10 +7865,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="H47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J47" s="12" t="s">
         <x:v>49</x:v>
@@ -7877,10 +7877,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L47" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N47" s="12" t="s">
         <x:v>49</x:v>
@@ -7889,22 +7889,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="P47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q47" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R47" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="T47" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="V47" s="12" t="s">
         <x:v>49</x:v>
@@ -7913,10 +7913,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="X47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z47" s="12" t="s">
         <x:v>49</x:v>
@@ -7925,10 +7925,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AB47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD47" s="12" t="s">
         <x:v>49</x:v>
@@ -7937,10 +7937,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AF47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH47" s="12" t="s">
         <x:v>49</x:v>
@@ -7949,10 +7949,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AJ47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL47" s="12" t="s">
         <x:v>49</x:v>
@@ -7961,22 +7961,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AN47" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="AR47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT47" s="12" t="s">
         <x:v>49</x:v>
@@ -7985,7 +7985,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AV47" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AW47" s="12" t="s">
         <x:v>49</x:v>
@@ -8000,7 +8000,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="BA47" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB47" s="12" t="s">
         <x:v>49</x:v>
@@ -8009,42 +8009,42 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="BD47" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF47" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG47" s="12">
-        <x:v>55</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="BH47" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="BI47" s="12">
-        <x:v>45</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="BJ47" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:62">
       <x:c r="A48" s="11" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="D48" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E48" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F48" s="12" t="s">
         <x:v>49</x:v>
@@ -8053,10 +8053,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H48" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I48" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J48" s="12" t="s">
         <x:v>49</x:v>
@@ -8065,7 +8065,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="L48" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M48" s="12" t="s">
         <x:v>59</x:v>
@@ -8077,22 +8077,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="P48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q48" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R48" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="T48" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U48" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="V48" s="12" t="s">
         <x:v>49</x:v>
@@ -8101,10 +8101,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="X48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y48" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z48" s="12" t="s">
         <x:v>49</x:v>
@@ -8113,10 +8113,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AB48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC48" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD48" s="12" t="s">
         <x:v>49</x:v>
@@ -8125,10 +8125,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AF48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH48" s="12" t="s">
         <x:v>49</x:v>
@@ -8137,10 +8137,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AJ48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK48" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL48" s="12" t="s">
         <x:v>49</x:v>
@@ -8149,22 +8149,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AN48" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AP48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AR48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS48" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT48" s="12" t="s">
         <x:v>49</x:v>
@@ -8173,7 +8173,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AV48" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW48" s="12" t="s">
         <x:v>49</x:v>
@@ -8185,10 +8185,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AZ48" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA48" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB48" s="12" t="s">
         <x:v>49</x:v>
@@ -8197,7 +8197,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="BD48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE48" s="12" t="s">
         <x:v>49</x:v>
@@ -8206,21 +8206,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG48" s="12">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="BH48" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BI48" s="12">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="BJ48" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:62">
       <x:c r="A49" s="11" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B49" s="12" t="s">
         <x:v>53</x:v>
@@ -8229,7 +8229,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="D49" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E49" s="12" t="s">
         <x:v>62</x:v>
@@ -8241,10 +8241,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="H49" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I49" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J49" s="12" t="s">
         <x:v>49</x:v>
@@ -8256,7 +8256,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M49" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N49" s="12" t="s">
         <x:v>49</x:v>
@@ -8265,22 +8265,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="P49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="R49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="S49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="T49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U49" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V49" s="12" t="s">
         <x:v>49</x:v>
@@ -8289,10 +8289,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="X49" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z49" s="12" t="s">
         <x:v>49</x:v>
@@ -8304,7 +8304,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AC49" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD49" s="12" t="s">
         <x:v>49</x:v>
@@ -8313,10 +8313,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AF49" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH49" s="12" t="s">
         <x:v>49</x:v>
@@ -8325,10 +8325,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AJ49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AL49" s="12" t="s">
         <x:v>49</x:v>
@@ -8337,22 +8337,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AN49" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AQ49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="AR49" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AT49" s="12" t="s">
         <x:v>49</x:v>
@@ -8361,10 +8361,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AV49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX49" s="12" t="s">
         <x:v>49</x:v>
@@ -8373,10 +8373,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AZ49" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BA49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BB49" s="12" t="s">
         <x:v>49</x:v>
@@ -8385,42 +8385,42 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="BD49" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BF49" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG49" s="12">
-        <x:v>15</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BH49" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="BI49" s="12">
-        <x:v>13</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="BJ49" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:62">
       <x:c r="A50" s="11" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B50" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C50" s="12">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E50" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F50" s="12" t="s">
         <x:v>49</x:v>
@@ -8429,10 +8429,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="H50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I50" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J50" s="12" t="s">
         <x:v>49</x:v>
@@ -8441,10 +8441,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="L50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N50" s="12" t="s">
         <x:v>49</x:v>
@@ -8453,22 +8453,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="P50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Q50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="S50" s="12">
         <x:v>38</x:v>
       </x:c>
       <x:c r="T50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="U50" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V50" s="12" t="s">
         <x:v>49</x:v>
@@ -8477,10 +8477,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="X50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z50" s="12" t="s">
         <x:v>49</x:v>
@@ -8489,7 +8489,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AB50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC50" s="12" t="s">
         <x:v>49</x:v>
@@ -8501,10 +8501,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AF50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG50" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH50" s="12" t="s">
         <x:v>49</x:v>
@@ -8513,10 +8513,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AJ50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK50" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL50" s="12" t="s">
         <x:v>49</x:v>
@@ -8525,22 +8525,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AN50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO50" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AQ50" s="12">
         <x:v>38</x:v>
       </x:c>
       <x:c r="AR50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS50" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT50" s="12" t="s">
         <x:v>49</x:v>
@@ -8549,10 +8549,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AV50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW50" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX50" s="12" t="s">
         <x:v>49</x:v>
@@ -8561,7 +8561,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AZ50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA50" s="12" t="s">
         <x:v>63</x:v>
@@ -8573,30 +8573,30 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="BD50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BE50" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF50" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG50" s="12">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BH50" s="12" t="s">
-        <x:v>86</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="BI50" s="12">
-        <x:v>38</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="BJ50" s="12" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:62">
       <x:c r="A51" s="11" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B51" s="12" t="s">
         <x:v>53</x:v>
@@ -8605,10 +8605,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F51" s="12" t="s">
         <x:v>49</x:v>
@@ -8629,10 +8629,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="L51" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N51" s="12" t="s">
         <x:v>49</x:v>
@@ -8641,7 +8641,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="P51" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q51" s="12" t="s">
         <x:v>49</x:v>
@@ -8653,10 +8653,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="T51" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="V51" s="12" t="s">
         <x:v>49</x:v>
@@ -8665,7 +8665,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="X51" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y51" s="12" t="s">
         <x:v>49</x:v>
@@ -8677,7 +8677,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AB51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC51" s="12" t="s">
         <x:v>59</x:v>
@@ -8692,7 +8692,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="AG51" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH51" s="12" t="s">
         <x:v>49</x:v>
@@ -8704,7 +8704,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AK51" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL51" s="12" t="s">
         <x:v>49</x:v>
@@ -8713,22 +8713,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AN51" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="AR51" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS51" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT51" s="12" t="s">
         <x:v>49</x:v>
@@ -8737,10 +8737,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AV51" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AW51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX51" s="12" t="s">
         <x:v>49</x:v>
@@ -8752,7 +8752,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="BA51" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB51" s="12" t="s">
         <x:v>49</x:v>
@@ -8761,7 +8761,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="BD51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BE51" s="12" t="s">
         <x:v>49</x:v>
@@ -8770,24 +8770,24 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG51" s="12">
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="BH51" s="12" t="s">
-        <x:v>134</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="BI51" s="12">
-        <x:v>6</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="BJ51" s="12" t="s">
-        <x:v>134</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:62">
       <x:c r="A52" s="11" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C52" s="12">
         <x:v>40</x:v>
@@ -8796,7 +8796,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F52" s="12" t="s">
         <x:v>49</x:v>
@@ -8808,7 +8808,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I52" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J52" s="12" t="s">
         <x:v>49</x:v>
@@ -8841,10 +8841,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="T52" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="U52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V52" s="12" t="s">
         <x:v>49</x:v>
@@ -8880,7 +8880,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AG52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH52" s="12" t="s">
         <x:v>49</x:v>
@@ -8892,7 +8892,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AK52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AL52" s="12" t="s">
         <x:v>49</x:v>
@@ -8904,7 +8904,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AO52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP52" s="12" t="s">
         <x:v>49</x:v>
@@ -8916,7 +8916,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AS52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AT52" s="12" t="s">
         <x:v>49</x:v>
@@ -8928,7 +8928,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AW52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AX52" s="12" t="s">
         <x:v>49</x:v>
@@ -8940,7 +8940,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BB52" s="12" t="s">
         <x:v>49</x:v>
@@ -8952,27 +8952,27 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BE52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF52" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG52" s="12">
-        <x:v>3</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="BH52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="BI52" s="12">
-        <x:v>3</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="BJ52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:62">
       <x:c r="A53" s="11" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B53" s="12" t="s">
         <x:v>53</x:v>
@@ -8996,7 +8996,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="I53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J53" s="12" t="s">
         <x:v>49</x:v>
@@ -9005,7 +9005,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="L53" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M53" s="12" t="s">
         <x:v>49</x:v>
@@ -9029,7 +9029,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="T53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="U53" s="12" t="s">
         <x:v>49</x:v>
@@ -9041,7 +9041,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="X53" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y53" s="12" t="s">
         <x:v>49</x:v>
@@ -9056,7 +9056,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AC53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD53" s="12" t="s">
         <x:v>49</x:v>
@@ -9065,10 +9065,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AF53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AG53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH53" s="12" t="s">
         <x:v>49</x:v>
@@ -9080,7 +9080,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AK53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL53" s="12" t="s">
         <x:v>49</x:v>
@@ -9101,10 +9101,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AR53" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AT53" s="12" t="s">
         <x:v>49</x:v>
@@ -9113,7 +9113,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AV53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW53" s="12" t="s">
         <x:v>49</x:v>
@@ -9125,10 +9125,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AZ53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BB53" s="12" t="s">
         <x:v>49</x:v>
@@ -9137,7 +9137,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="BD53" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BE53" s="12" t="s">
         <x:v>49</x:v>
@@ -9146,33 +9146,33 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG53" s="12">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BH53" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="BI53" s="12">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BJ53" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:62">
       <x:c r="A54" s="11" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B54" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="D54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E54" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F54" s="12" t="s">
         <x:v>49</x:v>
@@ -9181,22 +9181,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="L54" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N54" s="12" t="s">
         <x:v>49</x:v>
@@ -9205,22 +9205,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="P54" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="T54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V54" s="12" t="s">
         <x:v>49</x:v>
@@ -9229,10 +9229,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="X54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y54" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z54" s="12" t="s">
         <x:v>49</x:v>
@@ -9241,10 +9241,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AB54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC54" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD54" s="12" t="s">
         <x:v>49</x:v>
@@ -9253,10 +9253,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AF54" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH54" s="12" t="s">
         <x:v>49</x:v>
@@ -9265,10 +9265,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AJ54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK54" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL54" s="12" t="s">
         <x:v>49</x:v>
@@ -9277,22 +9277,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AN54" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO54" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP54" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="AR54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS54" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT54" s="12" t="s">
         <x:v>49</x:v>
@@ -9301,10 +9301,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AV54" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW54" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX54" s="12" t="s">
         <x:v>49</x:v>
@@ -9313,10 +9313,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AZ54" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB54" s="12" t="s">
         <x:v>49</x:v>
@@ -9325,25 +9325,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="BD54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE54" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF54" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG54" s="12">
-        <x:v>66</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="BH54" s="12" t="s">
-        <x:v>138</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BI54" s="12">
-        <x:v>58</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="BJ54" s="12" t="s">
-        <x:v>126</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:62">
@@ -9357,10 +9357,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="D55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E55" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F55" s="12" t="s">
         <x:v>49</x:v>
@@ -9384,7 +9384,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M55" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N55" s="12" t="s">
         <x:v>49</x:v>
@@ -9393,7 +9393,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="P55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q55" s="12" t="s">
         <x:v>49</x:v>
@@ -9408,7 +9408,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="U55" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V55" s="12" t="s">
         <x:v>49</x:v>
@@ -9417,7 +9417,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="X55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y55" s="12" t="s">
         <x:v>49</x:v>
@@ -9429,7 +9429,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AB55" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC55" s="12" t="s">
         <x:v>49</x:v>
@@ -9441,7 +9441,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AF55" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG55" s="12" t="s">
         <x:v>49</x:v>
@@ -9456,7 +9456,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AK55" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL55" s="12" t="s">
         <x:v>49</x:v>
@@ -9465,13 +9465,13 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AN55" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO55" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP55" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ55" s="12">
         <x:v>43</x:v>
@@ -9489,7 +9489,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AV55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AW55" s="12" t="s">
         <x:v>49</x:v>
@@ -9501,7 +9501,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AZ55" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA55" s="12" t="s">
         <x:v>49</x:v>
@@ -9513,7 +9513,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="BD55" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BE55" s="12" t="s">
         <x:v>49</x:v>
@@ -9522,16 +9522,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG55" s="12">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH55" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="BI55" s="12">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BJ55" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:62">
@@ -9545,10 +9545,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="D56" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E56" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F56" s="12" t="s">
         <x:v>49</x:v>
@@ -9557,22 +9557,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H56" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I56" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J56" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="L56" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M56" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N56" s="12" t="s">
         <x:v>49</x:v>
@@ -9581,22 +9581,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="P56" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q56" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R56" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="S56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="T56" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U56" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V56" s="12" t="s">
         <x:v>49</x:v>
@@ -9605,10 +9605,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="X56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y56" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Z56" s="12" t="s">
         <x:v>49</x:v>
@@ -9617,7 +9617,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AB56" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC56" s="12" t="s">
         <x:v>63</x:v>
@@ -9629,10 +9629,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AF56" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG56" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH56" s="12" t="s">
         <x:v>49</x:v>
@@ -9641,10 +9641,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AJ56" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK56" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AL56" s="12" t="s">
         <x:v>49</x:v>
@@ -9653,22 +9653,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AN56" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO56" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AP56" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AQ56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="AR56" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS56" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT56" s="12" t="s">
         <x:v>49</x:v>
@@ -9680,7 +9680,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="AW56" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AX56" s="12" t="s">
         <x:v>49</x:v>
@@ -9689,10 +9689,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AZ56" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA56" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB56" s="12" t="s">
         <x:v>49</x:v>
@@ -9710,16 +9710,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG56" s="12">
-        <x:v>92</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="BH56" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="BI56" s="12">
-        <x:v>71</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BJ56" s="12" t="s">
-        <x:v>141</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:62">
@@ -9733,10 +9733,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="D57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E57" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F57" s="12" t="s">
         <x:v>49</x:v>
@@ -9748,7 +9748,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="I57" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J57" s="12" t="s">
         <x:v>49</x:v>
@@ -9757,10 +9757,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N57" s="12" t="s">
         <x:v>49</x:v>
@@ -9769,7 +9769,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="P57" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q57" s="12" t="s">
         <x:v>49</x:v>
@@ -9781,10 +9781,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="T57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V57" s="12" t="s">
         <x:v>49</x:v>
@@ -9793,7 +9793,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="X57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y57" s="12" t="s">
         <x:v>49</x:v>
@@ -9805,7 +9805,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AB57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AC57" s="12" t="s">
         <x:v>49</x:v>
@@ -9817,7 +9817,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AF57" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AG57" s="12" t="s">
         <x:v>49</x:v>
@@ -9832,7 +9832,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AK57" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL57" s="12" t="s">
         <x:v>49</x:v>
@@ -9844,19 +9844,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AO57" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP57" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AQ57" s="12">
         <x:v>45</x:v>
       </x:c>
       <x:c r="AR57" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS57" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT57" s="12" t="s">
         <x:v>49</x:v>
@@ -9865,7 +9865,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AV57" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AW57" s="12" t="s">
         <x:v>49</x:v>
@@ -9877,10 +9877,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AZ57" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA57" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB57" s="12" t="s">
         <x:v>49</x:v>
@@ -9889,22 +9889,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="BD57" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE57" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF57" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG57" s="12">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BH57" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="BI57" s="12">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="BJ57" s="12" t="s">
         <x:v>95</x:v>
@@ -9921,10 +9921,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="D58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E58" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F58" s="12" t="s">
         <x:v>49</x:v>
@@ -9933,13 +9933,13 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H58" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I58" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J58" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K58" s="12">
         <x:v>46</x:v>
@@ -9948,7 +9948,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="M58" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N58" s="12" t="s">
         <x:v>49</x:v>
@@ -9957,22 +9957,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="P58" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Q58" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R58" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="S58" s="12">
         <x:v>46</x:v>
       </x:c>
       <x:c r="T58" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U58" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V58" s="12" t="s">
         <x:v>49</x:v>
@@ -9981,10 +9981,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="X58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y58" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Z58" s="12" t="s">
         <x:v>49</x:v>
@@ -9993,10 +9993,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AB58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC58" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD58" s="12" t="s">
         <x:v>49</x:v>
@@ -10005,10 +10005,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AF58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG58" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH58" s="12" t="s">
         <x:v>49</x:v>
@@ -10017,10 +10017,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AJ58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK58" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AL58" s="12" t="s">
         <x:v>49</x:v>
@@ -10029,22 +10029,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AN58" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AO58" s="12" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="AP58" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="AQ58" s="12">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AR58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS58" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AT58" s="12" t="s">
         <x:v>49</x:v>
@@ -10053,7 +10053,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AV58" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW58" s="12" t="s">
         <x:v>50</x:v>
@@ -10065,10 +10065,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AZ58" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BA58" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="BB58" s="12" t="s">
         <x:v>49</x:v>
@@ -10077,30 +10077,30 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="BD58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BE58" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BF58" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG58" s="12">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BH58" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="BI58" s="12">
-        <x:v>57</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="BJ58" s="12" t="s">
-        <x:v>126</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:62">
       <x:c r="A59" s="11" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B59" s="12" t="s">
         <x:v>53</x:v>
@@ -10124,7 +10124,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="I59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J59" s="12" t="s">
         <x:v>49</x:v>
@@ -10133,10 +10133,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="L59" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N59" s="12" t="s">
         <x:v>49</x:v>
@@ -10148,19 +10148,19 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="Q59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S59" s="12">
         <x:v>47</x:v>
       </x:c>
       <x:c r="T59" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V59" s="12" t="s">
         <x:v>49</x:v>
@@ -10172,7 +10172,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="Y59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z59" s="12" t="s">
         <x:v>49</x:v>
@@ -10181,10 +10181,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AB59" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD59" s="12" t="s">
         <x:v>49</x:v>
@@ -10193,10 +10193,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AF59" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AG59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH59" s="12" t="s">
         <x:v>49</x:v>
@@ -10205,10 +10205,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AJ59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL59" s="12" t="s">
         <x:v>49</x:v>
@@ -10217,22 +10217,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AN59" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO59" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ59" s="12">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AR59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT59" s="12" t="s">
         <x:v>49</x:v>
@@ -10241,10 +10241,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AV59" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX59" s="12" t="s">
         <x:v>49</x:v>
@@ -10265,7 +10265,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="BD59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE59" s="12" t="s">
         <x:v>59</x:v>
@@ -10274,21 +10274,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG59" s="12">
-        <x:v>41</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="BH59" s="12" t="s">
-        <x:v>104</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="BI59" s="12">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="BJ59" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:62">
       <x:c r="A60" s="11" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
         <x:v>53</x:v>
@@ -10297,7 +10297,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D60" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E60" s="12" t="s">
         <x:v>50</x:v>
@@ -10309,10 +10309,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H60" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I60" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J60" s="12" t="s">
         <x:v>49</x:v>
@@ -10321,7 +10321,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="L60" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M60" s="12" t="s">
         <x:v>49</x:v>
@@ -10333,7 +10333,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="P60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Q60" s="12" t="s">
         <x:v>49</x:v>
@@ -10348,7 +10348,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="U60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V60" s="12" t="s">
         <x:v>49</x:v>
@@ -10357,7 +10357,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="X60" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y60" s="12" t="s">
         <x:v>49</x:v>
@@ -10372,7 +10372,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="AC60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD60" s="12" t="s">
         <x:v>49</x:v>
@@ -10381,10 +10381,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AF60" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG60" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH60" s="12" t="s">
         <x:v>49</x:v>
@@ -10393,90 +10393,90 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AJ60" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK60" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AL60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AM60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AN60" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AO60" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AP60" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AQ60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AR60" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AS60" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AT60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AU60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AV60" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AW60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AX60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AY60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AZ60" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="BA60" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="BB60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="BC60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="BD60" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="AL60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AM60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AN60" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="AO60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AP60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AQ60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AR60" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="AS60" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="AT60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AU60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AV60" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="AW60" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="AX60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AY60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AZ60" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="BA60" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="BB60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="BC60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="BD60" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="BE60" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BF60" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG60" s="12">
-        <x:v>16</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="BH60" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="BI60" s="12">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="BJ60" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:62">
       <x:c r="A61" s="11" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B61" s="12" t="s">
         <x:v>53</x:v>
@@ -10485,10 +10485,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="D61" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E61" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F61" s="12" t="s">
         <x:v>49</x:v>
@@ -10509,130 +10509,130 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="L61" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="M61" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="N61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="O61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="P61" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="Q61" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="R61" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="S61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="T61" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="U61" s="12" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="V61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="W61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="X61" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="Y61" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Z61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AA61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AB61" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AC61" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="AD61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AE61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AF61" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="AG61" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="AH61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AI61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AJ61" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="AK61" s="12" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="M61" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="O61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="P61" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="Q61" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="R61" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="S61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="T61" s="12" t="s">
+      <x:c r="AL61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AM61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AN61" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="AO61" s="12" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="U61" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="V61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="W61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="X61" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="Y61" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="Z61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AA61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AB61" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="AC61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AD61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AE61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AF61" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="AG61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AH61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AI61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AJ61" s="12" t="s">
+      <x:c r="AP61" s="12" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="AQ61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AR61" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="AS61" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="AT61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AU61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AV61" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AW61" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AX61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AY61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AZ61" s="12" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="AK61" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="AL61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AM61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AN61" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="AO61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AP61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AQ61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AR61" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="AS61" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AT61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AU61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AV61" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="AW61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AX61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AY61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AZ61" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="BA61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BB61" s="12" t="s">
         <x:v>49</x:v>
@@ -10641,7 +10641,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BD61" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE61" s="12" t="s">
         <x:v>59</x:v>
@@ -10650,21 +10650,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG61" s="12">
-        <x:v>25</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="BH61" s="12" t="s">
-        <x:v>147</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="BI61" s="12">
-        <x:v>23</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BJ61" s="12" t="s">
-        <x:v>147</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:62">
       <x:c r="A62" s="11" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
         <x:v>53</x:v>
@@ -10673,198 +10673,198 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D62" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="H62" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I62" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="L62" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="O62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="P62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="S62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="T62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="W62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="X62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AA62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AB62" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC62" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AE62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AF62" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG62" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AI62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AJ62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK62" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AM62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AN62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AQ62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AR62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AU62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AV62" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AX62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AY62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AZ62" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BB62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BC62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="BD62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BF62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BG62" s="12">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH62" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="BI62" s="12">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BJ62" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:62">
       <x:c r="A63" s="11" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B63" s="12" t="s">
-        <x:v>124</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C63" s="12">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F63" s="12" t="s">
         <x:v>49</x:v>
@@ -10873,10 +10873,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J63" s="12" t="s">
         <x:v>49</x:v>
@@ -10885,10 +10885,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="L63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N63" s="12" t="s">
         <x:v>49</x:v>
@@ -10897,22 +10897,22 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="P63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="R63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="S63" s="12">
         <x:v>51</x:v>
       </x:c>
       <x:c r="T63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V63" s="12" t="s">
         <x:v>49</x:v>
@@ -10921,10 +10921,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="X63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Z63" s="12" t="s">
         <x:v>49</x:v>
@@ -10933,10 +10933,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AB63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD63" s="12" t="s">
         <x:v>49</x:v>
@@ -10945,10 +10945,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AF63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AG63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH63" s="12" t="s">
         <x:v>49</x:v>
@@ -10957,10 +10957,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AJ63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL63" s="12" t="s">
         <x:v>49</x:v>
@@ -10969,22 +10969,22 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AN63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO63" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AP63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AQ63" s="12">
         <x:v>51</x:v>
       </x:c>
       <x:c r="AR63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AT63" s="12" t="s">
         <x:v>49</x:v>
@@ -10993,10 +10993,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AV63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AW63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX63" s="12" t="s">
         <x:v>49</x:v>
@@ -11005,10 +11005,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AZ63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BB63" s="12" t="s">
         <x:v>49</x:v>
@@ -11017,30 +11017,30 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="BD63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BE63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF63" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG63" s="12">
-        <x:v>2</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="BH63" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BI63" s="12">
-        <x:v>2</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="BJ63" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:62">
       <x:c r="A64" s="11" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B64" s="12" t="s">
         <x:v>53</x:v>
@@ -11049,10 +11049,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="D64" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F64" s="12" t="s">
         <x:v>49</x:v>
@@ -11061,10 +11061,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H64" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I64" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J64" s="12" t="s">
         <x:v>49</x:v>
@@ -11073,7 +11073,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="L64" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M64" s="12" t="s">
         <x:v>49</x:v>
@@ -11085,7 +11085,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="P64" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q64" s="12" t="s">
         <x:v>49</x:v>
@@ -11097,10 +11097,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="T64" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U64" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V64" s="12" t="s">
         <x:v>49</x:v>
@@ -11121,10 +11121,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AB64" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AC64" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD64" s="12" t="s">
         <x:v>49</x:v>
@@ -11133,10 +11133,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AF64" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AG64" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH64" s="12" t="s">
         <x:v>49</x:v>
@@ -11145,7 +11145,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AJ64" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK64" s="12" t="s">
         <x:v>59</x:v>
@@ -11169,7 +11169,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AR64" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS64" s="12" t="s">
         <x:v>63</x:v>
@@ -11181,7 +11181,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AV64" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AW64" s="12" t="s">
         <x:v>50</x:v>
@@ -11193,10 +11193,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AZ64" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA64" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BB64" s="12" t="s">
         <x:v>49</x:v>
@@ -11205,7 +11205,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="BD64" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BE64" s="12" t="s">
         <x:v>59</x:v>
@@ -11214,21 +11214,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG64" s="12">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="BH64" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="BI64" s="12">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="BJ64" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:62">
       <x:c r="A65" s="11" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B65" s="12" t="s">
         <x:v>53</x:v>
@@ -11237,7 +11237,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="D65" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E65" s="12" t="s">
         <x:v>50</x:v>
@@ -11249,7 +11249,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="H65" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I65" s="12" t="s">
         <x:v>63</x:v>
@@ -11261,10 +11261,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="L65" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M65" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N65" s="12" t="s">
         <x:v>49</x:v>
@@ -11273,19 +11273,19 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="P65" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q65" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R65" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="S65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="T65" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="U65" s="12" t="s">
         <x:v>50</x:v>
@@ -11297,10 +11297,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="X65" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y65" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z65" s="12" t="s">
         <x:v>49</x:v>
@@ -11309,10 +11309,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AB65" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC65" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD65" s="12" t="s">
         <x:v>49</x:v>
@@ -11321,10 +11321,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AF65" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AG65" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH65" s="12" t="s">
         <x:v>49</x:v>
@@ -11333,7 +11333,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AJ65" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK65" s="12" t="s">
         <x:v>50</x:v>
@@ -11345,19 +11345,19 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AN65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AO65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AR65" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS65" s="12" t="s">
         <x:v>56</x:v>
@@ -11369,7 +11369,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AV65" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AW65" s="12" t="s">
         <x:v>49</x:v>
@@ -11381,10 +11381,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AZ65" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA65" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BB65" s="12" t="s">
         <x:v>49</x:v>
@@ -11393,30 +11393,30 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="BD65" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="BE65" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="BE65" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="BF65" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG65" s="12">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="BH65" s="12" t="s">
         <x:v>147</x:v>
       </x:c>
       <x:c r="BI65" s="12">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="BJ65" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:62">
       <x:c r="A66" s="11" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B66" s="12" t="s">
         <x:v>53</x:v>
@@ -11425,10 +11425,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="D66" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F66" s="12" t="s">
         <x:v>49</x:v>
@@ -11437,10 +11437,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H66" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I66" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J66" s="12" t="s">
         <x:v>49</x:v>
@@ -11461,7 +11461,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="P66" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q66" s="12" t="s">
         <x:v>49</x:v>
@@ -11476,7 +11476,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="U66" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V66" s="12" t="s">
         <x:v>49</x:v>
@@ -11485,7 +11485,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="X66" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y66" s="12" t="s">
         <x:v>49</x:v>
@@ -11500,7 +11500,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AC66" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD66" s="12" t="s">
         <x:v>49</x:v>
@@ -11509,10 +11509,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AF66" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG66" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH66" s="12" t="s">
         <x:v>49</x:v>
@@ -11521,10 +11521,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AJ66" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK66" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL66" s="12" t="s">
         <x:v>49</x:v>
@@ -11545,7 +11545,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AR66" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS66" s="12" t="s">
         <x:v>49</x:v>
@@ -11569,7 +11569,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AZ66" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA66" s="12" t="s">
         <x:v>49</x:v>
@@ -11581,7 +11581,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BD66" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BE66" s="12" t="s">
         <x:v>49</x:v>
@@ -11590,24 +11590,24 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG66" s="12">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BH66" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="BI66" s="12">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="BJ66" s="12" t="s">
-        <x:v>134</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:62">
       <x:c r="A67" s="11" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B67" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C67" s="12">
         <x:v>55</x:v>
@@ -11616,10 +11616,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G67" s="12">
         <x:v>55</x:v>
@@ -11628,10 +11628,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K67" s="12">
         <x:v>55</x:v>
@@ -11640,10 +11640,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="M67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="O67" s="12">
         <x:v>55</x:v>
@@ -11652,10 +11652,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Q67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S67" s="12">
         <x:v>55</x:v>
@@ -11664,10 +11664,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="U67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W67" s="12">
         <x:v>55</x:v>
@@ -11676,10 +11676,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Y67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA67" s="12">
         <x:v>55</x:v>
@@ -11688,10 +11688,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AC67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AE67" s="12">
         <x:v>55</x:v>
@@ -11700,10 +11700,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AG67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AI67" s="12">
         <x:v>55</x:v>
@@ -11712,10 +11712,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AK67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM67" s="12">
         <x:v>55</x:v>
@@ -11724,10 +11724,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AO67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ67" s="12">
         <x:v>55</x:v>
@@ -11736,10 +11736,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AS67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU67" s="12">
         <x:v>55</x:v>
@@ -11748,10 +11748,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AW67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY67" s="12">
         <x:v>55</x:v>
@@ -11760,10 +11760,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC67" s="12">
         <x:v>55</x:v>
@@ -11772,22 +11772,22 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BE67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG67" s="12">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BH67" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BI67" s="12">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BJ67" s="12" t="s">
-        <x:v>154</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:62">
@@ -11801,181 +11801,181 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="D68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="H68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="L68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="O68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="P68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="T68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="U68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="X68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AB68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AE68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AF68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AI68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AJ68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AN68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AR68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AT68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AV68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AZ68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BB68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="BD68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG68" s="12">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BH68" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="BI68" s="12">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BJ68" s="12" t="s">
-        <x:v>154</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:62">
